--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -321,16 +321,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -456,7 +456,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -809,10 +809,10 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:microbiology</t>
-  </si>
-  <si>
-    <t>microbiology</t>
+    <t>DiagnosticReport.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
   </si>
   <si>
     <t>診断レポートを作成した臨床分野、部門、または診断サービス（心臓病学、生化学、血液学、放射線医学など）を分類するコード</t>
@@ -824,43 +824,43 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:microbiology.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:microbiology.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:microbiology.coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:microbiology.coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:microbiology.coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:microbiology.coding.system</t>
+    <t>DiagnosticReport.category:first.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.system</t>
   </si>
   <si>
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:microbiology.coding.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:microbiology.coding.code</t>
+    <t>DiagnosticReport.category:first.coding.version</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.code</t>
   </si>
   <si>
     <t>LP7819-8</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:microbiology.coding.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:microbiology.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:microbiology.text</t>
+    <t>DiagnosticReport.category:first.coding.display</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.userSelected</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.text</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -1575,9 +1575,9 @@
   <dimension ref="A1:AN56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.28515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.01171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.8125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.8984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -277,7 +277,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
@@ -1575,17 +1575,17 @@
   <dimension ref="A1:AN56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.01171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.8125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.01953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="207.65625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="178.02734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1594,26 +1594,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="73.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.203125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="62.875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="147.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="104.53515625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
@@ -375,7 +375,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -591,7 +591,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -1076,7 +1076,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1121,7 +1121,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy)
+    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1202,7 +1202,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -1246,7 +1246,7 @@
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>

--- a/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
